--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -11052,7 +11052,7 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="H143" s="1">
-        <x:v>17260</x:v>
+        <x:v>37360</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:8">
